--- a/output/业务系统风险对照.xlsx
+++ b/output/业务系统风险对照.xlsx
@@ -461,44 +461,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>业务系统A</t>
+          <t>支付网关</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>业务系统B</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="n"/>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>业务系统D</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>业务系统C</t>
-        </is>
-      </c>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>电商平台</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>供应链平台</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OA系统</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -511,41 +527,81 @@
           <t>等级</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>等级</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10.18.135.26</t>
+          <t>10.10.2.21</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -553,523 +609,609 @@
           <t>严重</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.1</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>支付接口存在命令执行行为</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.11</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>商城应用出现异常WebShell活动</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.31</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>192.168.20.40</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>供应链门户存在异常登录行为</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.4.41</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>10.100.12.1</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>OA门户发现批量扫描行为</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10.18.135.30</t>
+          <t>10.10.2.22</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.2</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
           <t>严重</t>
         </is>
       </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>支付数据库疑似被提权访问</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.11</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>192.168.20.49</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
+          <t>商城应用反序列化漏洞</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.32</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>供应链任务节点出现异常脚本执行</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.4.42</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>低危</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>10.100.12.1</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>OA数据库存在可疑访问告警</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10.16.11.65</t>
+          <t>10.10.2.21</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>支付接口远程代码执行漏洞</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.12</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>商城数据库弱鉴权漏洞</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.31</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>供应链门户SQL注入漏洞</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>10.10.4.41</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.1</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>192.168.11.4</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>10.100.12.1</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>低危</t>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>OA门户跨站脚本漏洞</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10.18.20.115</t>
+          <t>10.10.2.22</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>支付数据库未授权访问漏洞</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.11</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>商城接口目录遍历漏洞</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.32</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.2</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>192.168.20.40</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>10.100.12.1</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>供应链任务服务默认口令风险</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>10.10.4.42</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>OA数据库版本过旧漏洞</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10.18.135.26</t>
+          <t>10.10.2.21</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>支付节点中间件信息泄露漏洞</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.12</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>商城任务组件信息泄露</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.3</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>低危</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>192.168.20.49</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>10.100.12.1</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>低危</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>10.18.135.30</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>172.16.8.161</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>192.168.11.4</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>10.18.20.115</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>低危</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.3</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>192.168.11.4</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>10.18.20.115</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.3</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>10.18.20.115</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.2</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>低危</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10.18.135.26</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>172.16.1.2</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10.18.135.30</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
+      <c r="Q13" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>总数</t>
+          <t>事件</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>总数</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>总数</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>总数</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="n">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="n">
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="n">
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
